--- a/artfynd/A 8541-2024 artfynd.xlsx
+++ b/artfynd/A 8541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,131 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133594177</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58502</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nämforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>593953</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7036160</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8541-2024 artfynd.xlsx
+++ b/artfynd/A 8541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104464411</v>
+        <v>133594177</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näsåker, Ång</t>
+          <t>Nämforsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593959.1680664871</v>
+        <v>593953</v>
       </c>
       <c r="R2" t="n">
-        <v>7036231.740210544</v>
+        <v>7036160</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,22 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,29 +778,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Nilsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133594177</v>
+        <v>97528289</v>
       </c>
       <c r="B3" t="n">
-        <v>58519</v>
+        <v>98186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,46 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nämforsen, Ång</t>
+          <t>Näsåker, hällristningsområdet vid Nämforsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593953</v>
+        <v>593914</v>
       </c>
       <c r="R3" t="n">
-        <v>7036160</v>
+        <v>7036225</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,27 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +882,125 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Invid stig</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97528293</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Näsåker, hällristningsområdet vid Nämforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593944</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7036125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Berghäll</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8541-2024 artfynd.xlsx
+++ b/artfynd/A 8541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133594177</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97528289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97528293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>